--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K314"/>
+  <dimension ref="A1:K315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12666,6 +12666,45 @@
         <v>301.71</v>
       </c>
       <c r="K314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>314.06</v>
+      </c>
+      <c r="C315" t="n">
+        <v>285.55</v>
+      </c>
+      <c r="D315" t="n">
+        <v>287.11</v>
+      </c>
+      <c r="E315" t="n">
+        <v>285.48</v>
+      </c>
+      <c r="F315" t="n">
+        <v>287.67</v>
+      </c>
+      <c r="G315" t="n">
+        <v>298.95</v>
+      </c>
+      <c r="H315" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="I315" t="n">
+        <v>310.23</v>
+      </c>
+      <c r="J315" t="n">
+        <v>305.32</v>
+      </c>
+      <c r="K315" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12682,7 +12721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15885,6 +15924,16 @@
       </c>
       <c r="B320" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -16053,28 +16102,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1004176047878607</v>
+        <v>0.1018211680461575</v>
       </c>
       <c r="J2" t="n">
+        <v>314</v>
+      </c>
+      <c r="K2" t="n">
         <v>313</v>
       </c>
-      <c r="K2" t="n">
-        <v>312</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0144320136922147</v>
+        <v>0.01493194470615566</v>
       </c>
       <c r="M2" t="n">
-        <v>4.581451617326358</v>
+        <v>4.573542882834842</v>
       </c>
       <c r="N2" t="n">
-        <v>34.61511588537273</v>
+        <v>34.51828530293849</v>
       </c>
       <c r="O2" t="n">
-        <v>5.883461216441622</v>
+        <v>5.875226404398258</v>
       </c>
       <c r="P2" t="n">
-        <v>309.342188820769</v>
+        <v>309.3270034518877</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16131,28 +16180,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2087356143877188</v>
+        <v>0.2073156935647444</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06214935133541077</v>
+        <v>0.06175007591743764</v>
       </c>
       <c r="M3" t="n">
-        <v>4.464601168135549</v>
+        <v>4.455707980442778</v>
       </c>
       <c r="N3" t="n">
-        <v>32.96054899941962</v>
+        <v>32.86960803679462</v>
       </c>
       <c r="O3" t="n">
-        <v>5.74112785081639</v>
+        <v>5.73320224977234</v>
       </c>
       <c r="P3" t="n">
-        <v>282.189559855105</v>
+        <v>282.2049334373821</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16209,28 +16258,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2568431622492717</v>
+        <v>0.2559082002494378</v>
       </c>
       <c r="J4" t="n">
+        <v>314</v>
+      </c>
+      <c r="K4" t="n">
         <v>313</v>
       </c>
-      <c r="K4" t="n">
-        <v>312</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07310005781629236</v>
+        <v>0.07308684400906496</v>
       </c>
       <c r="M4" t="n">
-        <v>5.107378315687169</v>
+        <v>5.09577068529084</v>
       </c>
       <c r="N4" t="n">
-        <v>41.48996976298908</v>
+        <v>41.3634024313458</v>
       </c>
       <c r="O4" t="n">
-        <v>6.441270818944743</v>
+        <v>6.431438597339308</v>
       </c>
       <c r="P4" t="n">
-        <v>281.7591633489798</v>
+        <v>281.769357344967</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16287,28 +16336,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1813609331424988</v>
+        <v>0.1826408192304838</v>
       </c>
       <c r="J5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03397198776902999</v>
+        <v>0.0346699087039346</v>
       </c>
       <c r="M5" t="n">
-        <v>5.461993120523293</v>
+        <v>5.448395259521914</v>
       </c>
       <c r="N5" t="n">
-        <v>46.37529862297441</v>
+        <v>46.23788793967642</v>
       </c>
       <c r="O5" t="n">
-        <v>6.809941161491368</v>
+        <v>6.799844699673399</v>
       </c>
       <c r="P5" t="n">
-        <v>278.8501363962341</v>
+        <v>278.8361623255424</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16365,28 +16414,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.123406957165283</v>
+        <v>0.1245342763990534</v>
       </c>
       <c r="J6" t="n">
+        <v>314</v>
+      </c>
+      <c r="K6" t="n">
         <v>313</v>
       </c>
-      <c r="K6" t="n">
-        <v>312</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01865293429281156</v>
+        <v>0.01912006020795087</v>
       </c>
       <c r="M6" t="n">
-        <v>4.93149209053199</v>
+        <v>4.919642048234199</v>
       </c>
       <c r="N6" t="n">
-        <v>39.74172584910433</v>
+        <v>39.62346155958166</v>
       </c>
       <c r="O6" t="n">
-        <v>6.30410388945997</v>
+        <v>6.294716956272272</v>
       </c>
       <c r="P6" t="n">
-        <v>282.7789718009432</v>
+        <v>282.7666805123695</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16443,28 +16492,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1118219972445102</v>
+        <v>0.1120861957029342</v>
       </c>
       <c r="J7" t="n">
+        <v>314</v>
+      </c>
+      <c r="K7" t="n">
         <v>313</v>
       </c>
-      <c r="K7" t="n">
-        <v>312</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01663693132020938</v>
+        <v>0.01683357063565205</v>
       </c>
       <c r="M7" t="n">
-        <v>4.768231536656379</v>
+        <v>4.754256177084038</v>
       </c>
       <c r="N7" t="n">
-        <v>36.65954977143466</v>
+        <v>36.54290478702441</v>
       </c>
       <c r="O7" t="n">
-        <v>6.054713021393719</v>
+        <v>6.045072769373783</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6307300549931</v>
+        <v>295.6278494694447</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16521,28 +16570,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.091744039977518</v>
+        <v>0.09203149746271411</v>
       </c>
       <c r="J8" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009449238546640371</v>
+        <v>0.00957623091522164</v>
       </c>
       <c r="M8" t="n">
-        <v>5.411252885286799</v>
+        <v>5.395309105231663</v>
       </c>
       <c r="N8" t="n">
-        <v>43.87942598494003</v>
+        <v>43.73935505652056</v>
       </c>
       <c r="O8" t="n">
-        <v>6.62415473739405</v>
+        <v>6.613573546617634</v>
       </c>
       <c r="P8" t="n">
-        <v>297.5784250891043</v>
+        <v>297.5752928421913</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16599,28 +16648,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1768214409576868</v>
+        <v>0.1801781127115273</v>
       </c>
       <c r="J9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04246978494456</v>
+        <v>0.04423761024699757</v>
       </c>
       <c r="M9" t="n">
-        <v>4.584050311262611</v>
+        <v>4.58489161351772</v>
       </c>
       <c r="N9" t="n">
-        <v>35.05642049047353</v>
+        <v>35.02154480969875</v>
       </c>
       <c r="O9" t="n">
-        <v>5.920846264722091</v>
+        <v>5.91790037172803</v>
       </c>
       <c r="P9" t="n">
-        <v>300.6521216817119</v>
+        <v>300.6155460999989</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16677,28 +16726,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005476108495891648</v>
+        <v>0.004815344390040061</v>
       </c>
       <c r="J10" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L10" t="n">
-        <v>1.943270614768178e-05</v>
+        <v>1.513458743229723e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>6.560682312468622</v>
+        <v>6.542037417967697</v>
       </c>
       <c r="N10" t="n">
-        <v>76.74103608833832</v>
+        <v>76.49807378265466</v>
       </c>
       <c r="O10" t="n">
-        <v>8.760196121568187</v>
+        <v>8.746317727058322</v>
       </c>
       <c r="P10" t="n">
-        <v>306.1532496266278</v>
+        <v>306.1604495655312</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16736,7 +16785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K314"/>
+  <dimension ref="A1:K315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34589,6 +34638,63 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.56017931217896,174.50871313644055</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.56071759393433,174.5079487133606</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-35.56148952415049,174.50756727496577</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-35.56229482644595,174.50732299610766</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-35.563122146094756,174.50723614852507</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-35.56401576037869,174.5074638226458</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-35.56481130365217,174.50804636189417</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-35.56536824488373,174.50889107142538</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-35.56574525923433,174.50973552912671</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K315"/>
+  <dimension ref="A1:K316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12705,6 +12705,45 @@
         <v>305.32</v>
       </c>
       <c r="K315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>313.39</v>
+      </c>
+      <c r="C316" t="n">
+        <v>286.76</v>
+      </c>
+      <c r="D316" t="n">
+        <v>287.36</v>
+      </c>
+      <c r="E316" t="n">
+        <v>285.86</v>
+      </c>
+      <c r="F316" t="n">
+        <v>289.32</v>
+      </c>
+      <c r="G316" t="n">
+        <v>299.55</v>
+      </c>
+      <c r="H316" t="n">
+        <v>301.56</v>
+      </c>
+      <c r="I316" t="n">
+        <v>311.32</v>
+      </c>
+      <c r="J316" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="K316" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12721,7 +12760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B321"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15934,6 +15973,16 @@
       </c>
       <c r="B321" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -16102,28 +16151,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1018211680461575</v>
+        <v>0.102753629896903</v>
       </c>
       <c r="J2" t="n">
+        <v>315</v>
+      </c>
+      <c r="K2" t="n">
         <v>314</v>
       </c>
-      <c r="K2" t="n">
-        <v>313</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01493194470615566</v>
+        <v>0.015308309028217</v>
       </c>
       <c r="M2" t="n">
-        <v>4.573542882834842</v>
+        <v>4.563397576112603</v>
       </c>
       <c r="N2" t="n">
-        <v>34.51828530293849</v>
+        <v>34.41443530284765</v>
       </c>
       <c r="O2" t="n">
-        <v>5.875226404398258</v>
+        <v>5.866381789727605</v>
       </c>
       <c r="P2" t="n">
-        <v>309.3270034518877</v>
+        <v>309.3168787984199</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16180,28 +16229,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2073156935647444</v>
+        <v>0.2067146661072171</v>
       </c>
       <c r="J3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06175007591743764</v>
+        <v>0.06182801609355049</v>
       </c>
       <c r="M3" t="n">
-        <v>4.455707980442778</v>
+        <v>4.443798209259067</v>
       </c>
       <c r="N3" t="n">
-        <v>32.86960803679462</v>
+        <v>32.76777667790716</v>
       </c>
       <c r="O3" t="n">
-        <v>5.73320224977234</v>
+        <v>5.724314515984177</v>
       </c>
       <c r="P3" t="n">
-        <v>282.2049334373821</v>
+        <v>282.2114640378397</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16258,28 +16307,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2559082002494378</v>
+        <v>0.2551354975793946</v>
       </c>
       <c r="J4" t="n">
+        <v>315</v>
+      </c>
+      <c r="K4" t="n">
         <v>314</v>
       </c>
-      <c r="K4" t="n">
-        <v>313</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07308684400906496</v>
+        <v>0.07316252768481191</v>
       </c>
       <c r="M4" t="n">
-        <v>5.09577068529084</v>
+        <v>5.083389544489465</v>
       </c>
       <c r="N4" t="n">
-        <v>41.3634024313458</v>
+        <v>41.23576716721576</v>
       </c>
       <c r="O4" t="n">
-        <v>6.431438597339308</v>
+        <v>6.421508169208832</v>
       </c>
       <c r="P4" t="n">
-        <v>281.769357344967</v>
+        <v>281.777812026347</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16336,28 +16385,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1826408192304838</v>
+        <v>0.1841491436400526</v>
       </c>
       <c r="J5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0346699087039346</v>
+        <v>0.03546054084658978</v>
       </c>
       <c r="M5" t="n">
-        <v>5.448395259521914</v>
+        <v>5.4355247683002</v>
       </c>
       <c r="N5" t="n">
-        <v>46.23788793967642</v>
+        <v>46.10577544639276</v>
       </c>
       <c r="O5" t="n">
-        <v>6.799844699673399</v>
+        <v>6.790123374902164</v>
       </c>
       <c r="P5" t="n">
-        <v>278.8361623255424</v>
+        <v>278.8196356729472</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16414,28 +16463,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1245342763990534</v>
+        <v>0.1267547072943493</v>
       </c>
       <c r="J6" t="n">
+        <v>315</v>
+      </c>
+      <c r="K6" t="n">
         <v>314</v>
       </c>
-      <c r="K6" t="n">
-        <v>313</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01912006020795087</v>
+        <v>0.0199190571412966</v>
       </c>
       <c r="M6" t="n">
-        <v>4.919642048234199</v>
+        <v>4.911585781766142</v>
       </c>
       <c r="N6" t="n">
-        <v>39.62346155958166</v>
+        <v>39.53108935734789</v>
       </c>
       <c r="O6" t="n">
-        <v>6.294716956272272</v>
+        <v>6.287375394975864</v>
       </c>
       <c r="P6" t="n">
-        <v>282.7666805123695</v>
+        <v>282.7423852219898</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16492,28 +16541,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1120861957029342</v>
+        <v>0.1127448651888475</v>
       </c>
       <c r="J7" t="n">
+        <v>315</v>
+      </c>
+      <c r="K7" t="n">
         <v>314</v>
       </c>
-      <c r="K7" t="n">
-        <v>313</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01683357063565205</v>
+        <v>0.01714925675805268</v>
       </c>
       <c r="M7" t="n">
-        <v>4.754256177084038</v>
+        <v>4.742246908658291</v>
       </c>
       <c r="N7" t="n">
-        <v>36.54290478702441</v>
+        <v>36.42950186847294</v>
       </c>
       <c r="O7" t="n">
-        <v>6.045072769373783</v>
+        <v>6.035685699941054</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6278494694447</v>
+        <v>295.6206425050405</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16570,28 +16619,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09203149746271411</v>
+        <v>0.0930925469497145</v>
       </c>
       <c r="J8" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K8" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00957623091522164</v>
+        <v>0.009865029582087903</v>
       </c>
       <c r="M8" t="n">
-        <v>5.395309105231663</v>
+        <v>5.383187509669691</v>
       </c>
       <c r="N8" t="n">
-        <v>43.73935505652056</v>
+        <v>43.60736433677845</v>
       </c>
       <c r="O8" t="n">
-        <v>6.613573546617634</v>
+        <v>6.60358723246528</v>
       </c>
       <c r="P8" t="n">
-        <v>297.5752928421913</v>
+        <v>297.5636901140256</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16648,28 +16697,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1801781127115273</v>
+        <v>0.1842220130614088</v>
       </c>
       <c r="J9" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K9" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04423761024699757</v>
+        <v>0.0463308973618014</v>
       </c>
       <c r="M9" t="n">
-        <v>4.58489161351772</v>
+        <v>4.589105180093723</v>
       </c>
       <c r="N9" t="n">
-        <v>35.02154480969875</v>
+        <v>35.02225078890901</v>
       </c>
       <c r="O9" t="n">
-        <v>5.91790037172803</v>
+        <v>5.917960019205013</v>
       </c>
       <c r="P9" t="n">
-        <v>300.6155460999989</v>
+        <v>300.5713254702698</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16726,28 +16775,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004815344390040061</v>
+        <v>0.004822450741155843</v>
       </c>
       <c r="J10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K10" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L10" t="n">
-        <v>1.513458743229723e-05</v>
+        <v>1.52898141914104e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>6.542037417967697</v>
+        <v>6.521177382756385</v>
       </c>
       <c r="N10" t="n">
-        <v>76.49807378265466</v>
+        <v>76.25367133872501</v>
       </c>
       <c r="O10" t="n">
-        <v>8.746317727058322</v>
+        <v>8.732334815999957</v>
       </c>
       <c r="P10" t="n">
-        <v>306.1604495655312</v>
+        <v>306.1603718565635</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16785,7 +16834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K315"/>
+  <dimension ref="A1:K316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34695,6 +34744,63 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.56017624780078,174.50870676708968</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.56072244904766,174.50796066675773</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-35.56149019081255,174.50756990954844</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-35.56229536158497,174.50732713686634</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-35.5631222537983,174.5072543513415</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-35.56401406973241,174.50747011041105</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-35.564804825133876,174.50805640758603</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-35.565360168176426,174.50889792003224</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-35.56573721987919,174.50974001130743</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K316"/>
+  <dimension ref="A1:K317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12746,6 +12746,45 @@
       <c r="K316" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="C317" t="n">
+        <v>291.03</v>
+      </c>
+      <c r="D317" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="E317" t="n">
+        <v>286.56</v>
+      </c>
+      <c r="F317" t="n">
+        <v>291.09</v>
+      </c>
+      <c r="G317" t="n">
+        <v>299.34</v>
+      </c>
+      <c r="H317" t="n">
+        <v>302.24</v>
+      </c>
+      <c r="I317" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="J317" t="n">
+        <v>312.62</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12760,7 +12799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15983,6 +16022,16 @@
       </c>
       <c r="B322" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -16151,28 +16200,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.102753629896903</v>
+        <v>0.1051714873103098</v>
       </c>
       <c r="J2" t="n">
+        <v>316</v>
+      </c>
+      <c r="K2" t="n">
         <v>315</v>
       </c>
-      <c r="K2" t="n">
-        <v>314</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.015308309028217</v>
+        <v>0.01612170052656992</v>
       </c>
       <c r="M2" t="n">
-        <v>4.563397576112603</v>
+        <v>4.560220937901112</v>
       </c>
       <c r="N2" t="n">
-        <v>34.41443530284765</v>
+        <v>34.34595685270612</v>
       </c>
       <c r="O2" t="n">
-        <v>5.866381789727605</v>
+        <v>5.860542368476327</v>
       </c>
       <c r="P2" t="n">
-        <v>309.3168787984199</v>
+        <v>309.2905093375991</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16229,28 +16278,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2067146661072171</v>
+        <v>0.2089713459957683</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06182801609355049</v>
+        <v>0.0634668722257864</v>
       </c>
       <c r="M3" t="n">
-        <v>4.443798209259067</v>
+        <v>4.442547838829908</v>
       </c>
       <c r="N3" t="n">
-        <v>32.76777667790716</v>
+        <v>32.69946409387818</v>
       </c>
       <c r="O3" t="n">
-        <v>5.724314515984177</v>
+        <v>5.718344523887851</v>
       </c>
       <c r="P3" t="n">
-        <v>282.2114640378397</v>
+        <v>282.1868353908964</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16307,28 +16356,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2551354975793946</v>
+        <v>0.2544519145788076</v>
       </c>
       <c r="J4" t="n">
+        <v>316</v>
+      </c>
+      <c r="K4" t="n">
         <v>315</v>
       </c>
-      <c r="K4" t="n">
-        <v>314</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07316252768481191</v>
+        <v>0.0732894430665656</v>
       </c>
       <c r="M4" t="n">
-        <v>5.083389544489465</v>
+        <v>5.07060895903916</v>
       </c>
       <c r="N4" t="n">
-        <v>41.23576716721576</v>
+        <v>41.10805643480442</v>
       </c>
       <c r="O4" t="n">
-        <v>6.421508169208832</v>
+        <v>6.411556475209776</v>
       </c>
       <c r="P4" t="n">
-        <v>281.777812026347</v>
+        <v>281.7853242962453</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16385,28 +16434,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1841491436400526</v>
+        <v>0.1861047369117691</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03546054084658978</v>
+        <v>0.03642605464991433</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4355247683002</v>
+        <v>5.423989229531973</v>
       </c>
       <c r="N5" t="n">
-        <v>46.10577544639276</v>
+        <v>45.9851139844984</v>
       </c>
       <c r="O5" t="n">
-        <v>6.790123374902164</v>
+        <v>6.781232482705367</v>
       </c>
       <c r="P5" t="n">
-        <v>278.8196356729472</v>
+        <v>278.7981143557837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16463,28 +16512,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1267547072943493</v>
+        <v>0.1301465118571158</v>
       </c>
       <c r="J6" t="n">
+        <v>316</v>
+      </c>
+      <c r="K6" t="n">
         <v>315</v>
       </c>
-      <c r="K6" t="n">
-        <v>314</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0199190571412966</v>
+        <v>0.02108618479441349</v>
       </c>
       <c r="M6" t="n">
-        <v>4.911585781766142</v>
+        <v>4.907924669639073</v>
       </c>
       <c r="N6" t="n">
-        <v>39.53108935734789</v>
+        <v>39.48428918678206</v>
       </c>
       <c r="O6" t="n">
-        <v>6.287375394975864</v>
+        <v>6.283652535490967</v>
       </c>
       <c r="P6" t="n">
-        <v>282.7423852219898</v>
+        <v>282.7051108144981</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16541,28 +16590,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1127448651888475</v>
+        <v>0.1132478820990795</v>
       </c>
       <c r="J7" t="n">
+        <v>316</v>
+      </c>
+      <c r="K7" t="n">
         <v>315</v>
       </c>
-      <c r="K7" t="n">
-        <v>314</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01714925675805268</v>
+        <v>0.01742393101381667</v>
       </c>
       <c r="M7" t="n">
-        <v>4.742246908658291</v>
+        <v>4.729558420827044</v>
       </c>
       <c r="N7" t="n">
-        <v>36.42950186847294</v>
+        <v>36.31558347899508</v>
       </c>
       <c r="O7" t="n">
-        <v>6.035685699941054</v>
+        <v>6.026241239694532</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6206425050405</v>
+        <v>295.6151145753087</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16619,28 +16668,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0930925469497145</v>
+        <v>0.094597201267122</v>
       </c>
       <c r="J8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K8" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009865029582087903</v>
+        <v>0.01025349205697812</v>
       </c>
       <c r="M8" t="n">
-        <v>5.383187509669691</v>
+        <v>5.373260352417128</v>
       </c>
       <c r="N8" t="n">
-        <v>43.60736433677845</v>
+        <v>43.48403300648884</v>
       </c>
       <c r="O8" t="n">
-        <v>6.60358723246528</v>
+        <v>6.594242413385243</v>
       </c>
       <c r="P8" t="n">
-        <v>297.5636901140256</v>
+        <v>297.5471641864706</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16697,28 +16746,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1842220130614088</v>
+        <v>0.1877212018598608</v>
       </c>
       <c r="J9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0463308973618014</v>
+        <v>0.04824681577054601</v>
       </c>
       <c r="M9" t="n">
-        <v>4.589105180093723</v>
+        <v>4.5907552710932</v>
       </c>
       <c r="N9" t="n">
-        <v>35.02225078890901</v>
+        <v>34.99479046641039</v>
       </c>
       <c r="O9" t="n">
-        <v>5.917960019205013</v>
+        <v>5.915639480767095</v>
       </c>
       <c r="P9" t="n">
-        <v>300.5713254702698</v>
+        <v>300.5328931606586</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16775,28 +16824,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004822450741155843</v>
+        <v>0.009109029474157098</v>
       </c>
       <c r="J10" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K10" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L10" t="n">
-        <v>1.52898141914104e-05</v>
+        <v>5.485872604271691e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>6.521177382756385</v>
+        <v>6.525235877263738</v>
       </c>
       <c r="N10" t="n">
-        <v>76.25367133872501</v>
+        <v>76.13699532611275</v>
       </c>
       <c r="O10" t="n">
-        <v>8.732334815999957</v>
+        <v>8.725651570290482</v>
       </c>
       <c r="P10" t="n">
-        <v>306.1603718565635</v>
+        <v>306.1132914815028</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16834,7 +16883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K316"/>
+  <dimension ref="A1:K317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34801,6 +34850,63 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.56018649288466,174.50872806163775</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.560739582371674,174.50800284941826</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-35.561490564143284,174.50757138491474</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-35.562296347366996,174.5073347645798</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-35.563122369331786,174.50727387799904</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-35.56401466145865,174.50746790969328</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-35.56480102738141,174.5080622964391</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-35.565365503249176,174.50889339618197</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-35.56568537423824,174.50976891677828</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K317"/>
+  <dimension ref="A1:K318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12785,6 +12785,45 @@
       <c r="K317" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="C318" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="D318" t="n">
+        <v>289.84</v>
+      </c>
+      <c r="E318" t="n">
+        <v>286.37</v>
+      </c>
+      <c r="F318" t="n">
+        <v>291.26</v>
+      </c>
+      <c r="G318" t="n">
+        <v>300.13</v>
+      </c>
+      <c r="H318" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="I318" t="n">
+        <v>305.88</v>
+      </c>
+      <c r="J318" t="n">
+        <v>313.63</v>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16032,6 +16071,16 @@
       </c>
       <c r="B323" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -16200,28 +16249,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1051714873103098</v>
+        <v>0.1091452759959297</v>
       </c>
       <c r="J2" t="n">
+        <v>317</v>
+      </c>
+      <c r="K2" t="n">
         <v>316</v>
       </c>
-      <c r="K2" t="n">
-        <v>315</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01612170052656992</v>
+        <v>0.01741314547798023</v>
       </c>
       <c r="M2" t="n">
-        <v>4.560220937901112</v>
+        <v>4.564060626032545</v>
       </c>
       <c r="N2" t="n">
-        <v>34.34595685270612</v>
+        <v>34.3462545401062</v>
       </c>
       <c r="O2" t="n">
-        <v>5.860542368476327</v>
+        <v>5.860567766019449</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2905093375991</v>
+        <v>309.2469065407032</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16278,28 +16327,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2089713459957683</v>
+        <v>0.2123522601899322</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0634668722257864</v>
+        <v>0.06570654475867477</v>
       </c>
       <c r="M3" t="n">
-        <v>4.442547838829908</v>
+        <v>4.447461702325208</v>
       </c>
       <c r="N3" t="n">
-        <v>32.69946409387818</v>
+        <v>32.67490404994816</v>
       </c>
       <c r="O3" t="n">
-        <v>5.718344523887851</v>
+        <v>5.71619664199441</v>
       </c>
       <c r="P3" t="n">
-        <v>282.1868353908964</v>
+        <v>282.1497134574997</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16356,28 +16405,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2544519145788076</v>
+        <v>0.2553383099521899</v>
       </c>
       <c r="J4" t="n">
+        <v>317</v>
+      </c>
+      <c r="K4" t="n">
         <v>316</v>
       </c>
-      <c r="K4" t="n">
-        <v>315</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0732894430665656</v>
+        <v>0.07426298168046075</v>
       </c>
       <c r="M4" t="n">
-        <v>5.07060895903916</v>
+        <v>5.05844874116033</v>
       </c>
       <c r="N4" t="n">
-        <v>41.10805643480442</v>
+        <v>40.98328611925579</v>
       </c>
       <c r="O4" t="n">
-        <v>6.411556475209776</v>
+        <v>6.401818969578551</v>
       </c>
       <c r="P4" t="n">
-        <v>281.7853242962453</v>
+        <v>281.7755246525799</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16434,28 +16483,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1861047369117691</v>
+        <v>0.1878947208260605</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03642605464991433</v>
+        <v>0.03735284206149181</v>
       </c>
       <c r="M5" t="n">
-        <v>5.423989229531973</v>
+        <v>5.41192861338403</v>
       </c>
       <c r="N5" t="n">
-        <v>45.9851139844984</v>
+        <v>45.86082639212425</v>
       </c>
       <c r="O5" t="n">
-        <v>6.781232482705367</v>
+        <v>6.772062196415819</v>
       </c>
       <c r="P5" t="n">
-        <v>278.7981143557837</v>
+        <v>278.7782968440462</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16512,28 +16561,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1301465118571158</v>
+        <v>0.1336140267572875</v>
       </c>
       <c r="J6" t="n">
+        <v>317</v>
+      </c>
+      <c r="K6" t="n">
         <v>316</v>
       </c>
-      <c r="K6" t="n">
-        <v>315</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02108618479441349</v>
+        <v>0.02231604540808751</v>
       </c>
       <c r="M6" t="n">
-        <v>4.907924669639073</v>
+        <v>4.904405120301067</v>
       </c>
       <c r="N6" t="n">
-        <v>39.48428918678206</v>
+        <v>39.44072842257424</v>
       </c>
       <c r="O6" t="n">
-        <v>6.283652535490967</v>
+        <v>6.280185381226755</v>
       </c>
       <c r="P6" t="n">
-        <v>282.7051108144981</v>
+        <v>282.6667753138323</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16590,28 +16639,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1132478820990795</v>
+        <v>0.1142716454489732</v>
       </c>
       <c r="J7" t="n">
+        <v>317</v>
+      </c>
+      <c r="K7" t="n">
         <v>316</v>
       </c>
-      <c r="K7" t="n">
-        <v>315</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01742393101381667</v>
+        <v>0.01786108548637055</v>
       </c>
       <c r="M7" t="n">
-        <v>4.729558420827044</v>
+        <v>4.719329659143863</v>
       </c>
       <c r="N7" t="n">
-        <v>36.31558347899508</v>
+        <v>36.20775539623028</v>
       </c>
       <c r="O7" t="n">
-        <v>6.026241239694532</v>
+        <v>6.017288043315716</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6151145753087</v>
+        <v>295.6037962445411</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16668,28 +16717,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.094597201267122</v>
+        <v>0.09652590994023143</v>
       </c>
       <c r="J8" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K8" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01025349205697812</v>
+        <v>0.01074370478535991</v>
       </c>
       <c r="M8" t="n">
-        <v>5.373260352417128</v>
+        <v>5.36535015024493</v>
       </c>
       <c r="N8" t="n">
-        <v>43.48403300648884</v>
+        <v>43.37126382417383</v>
       </c>
       <c r="O8" t="n">
-        <v>6.594242413385243</v>
+        <v>6.585686283461567</v>
       </c>
       <c r="P8" t="n">
-        <v>297.5471641864706</v>
+        <v>297.5258528056606</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16746,28 +16795,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1877212018598608</v>
+        <v>0.187965854694511</v>
       </c>
       <c r="J9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K9" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04824681577054601</v>
+        <v>0.04870836619965979</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5907552710932</v>
+        <v>4.577300301075919</v>
       </c>
       <c r="N9" t="n">
-        <v>34.99479046641039</v>
+        <v>34.88410258463632</v>
       </c>
       <c r="O9" t="n">
-        <v>5.915639480767095</v>
+        <v>5.906276541496878</v>
       </c>
       <c r="P9" t="n">
-        <v>300.5328931606586</v>
+        <v>300.5301898546601</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16824,28 +16873,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009109029474157098</v>
+        <v>0.01405271192629477</v>
       </c>
       <c r="J10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L10" t="n">
-        <v>5.485872604271691e-05</v>
+        <v>0.0001312377471650583</v>
       </c>
       <c r="M10" t="n">
-        <v>6.525235877263738</v>
+        <v>6.532813353190098</v>
       </c>
       <c r="N10" t="n">
-        <v>76.13699532611275</v>
+        <v>76.06135069457191</v>
       </c>
       <c r="O10" t="n">
-        <v>8.725651570290482</v>
+        <v>8.721315880907646</v>
       </c>
       <c r="P10" t="n">
-        <v>306.1132914815028</v>
+        <v>306.0586659692053</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16883,7 +16932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K317"/>
+  <dimension ref="A1:K318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34907,6 +34956,63 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.56019724107114,174.5087504019059</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.56074648384683,174.5080198410336</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.561496804097054,174.50759604461075</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.56229607979764,174.50733269420044</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-35.563122380428055,174.5072757534407</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-35.56401243544071,174.50747618858387</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-35.56479734132728,174.5080680120901</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-35.56540047761104,174.50886373981564</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-35.56567708877922,174.50977353616187</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K318"/>
+  <dimension ref="A1:K319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12824,6 +12824,45 @@
       <c r="K318" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>314.65</v>
+      </c>
+      <c r="C319" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="D319" t="n">
+        <v>288.97</v>
+      </c>
+      <c r="E319" t="n">
+        <v>285.09</v>
+      </c>
+      <c r="F319" t="n">
+        <v>289.51</v>
+      </c>
+      <c r="G319" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="H319" t="n">
+        <v>303.03</v>
+      </c>
+      <c r="I319" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="J319" t="n">
+        <v>306.46</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12838,7 +12877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16081,6 +16120,16 @@
       </c>
       <c r="B324" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -16249,28 +16298,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1091452759959297</v>
+        <v>0.1108206567215052</v>
       </c>
       <c r="J2" t="n">
+        <v>318</v>
+      </c>
+      <c r="K2" t="n">
         <v>317</v>
       </c>
-      <c r="K2" t="n">
-        <v>316</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01741314547798023</v>
+        <v>0.01806228226270679</v>
       </c>
       <c r="M2" t="n">
-        <v>4.564060626032545</v>
+        <v>4.557295530322479</v>
       </c>
       <c r="N2" t="n">
-        <v>34.3462545401062</v>
+        <v>34.25739348634124</v>
       </c>
       <c r="O2" t="n">
-        <v>5.860567766019449</v>
+        <v>5.852981589441508</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2469065407032</v>
+        <v>309.2284759850105</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16327,28 +16376,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2123522601899322</v>
+        <v>0.2145316886251446</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06570654475867477</v>
+        <v>0.06737016535917972</v>
       </c>
       <c r="M3" t="n">
-        <v>4.447461702325208</v>
+        <v>4.445735699672177</v>
       </c>
       <c r="N3" t="n">
-        <v>32.67490404994816</v>
+        <v>32.60500410376095</v>
       </c>
       <c r="O3" t="n">
-        <v>5.71619664199441</v>
+        <v>5.710079167906602</v>
       </c>
       <c r="P3" t="n">
-        <v>282.1497134574997</v>
+        <v>282.1257224292924</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16405,28 +16454,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2553383099521899</v>
+        <v>0.2556101048098522</v>
       </c>
       <c r="J4" t="n">
+        <v>318</v>
+      </c>
+      <c r="K4" t="n">
         <v>317</v>
       </c>
-      <c r="K4" t="n">
-        <v>316</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07426298168046075</v>
+        <v>0.0749204729388685</v>
       </c>
       <c r="M4" t="n">
-        <v>5.05844874116033</v>
+        <v>5.043672420571111</v>
       </c>
       <c r="N4" t="n">
-        <v>40.98328611925579</v>
+        <v>40.85450432093718</v>
       </c>
       <c r="O4" t="n">
-        <v>6.401818969578551</v>
+        <v>6.391752836346003</v>
       </c>
       <c r="P4" t="n">
-        <v>281.7755246525799</v>
+        <v>281.7725121728087</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16483,28 +16532,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1878947208260605</v>
+        <v>0.1887811901072252</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03735284206149181</v>
+        <v>0.03795800190477427</v>
       </c>
       <c r="M5" t="n">
-        <v>5.41192861338403</v>
+        <v>5.397325592053587</v>
       </c>
       <c r="N5" t="n">
-        <v>45.86082639212425</v>
+        <v>45.7210500033449</v>
       </c>
       <c r="O5" t="n">
-        <v>6.772062196415819</v>
+        <v>6.761734245246918</v>
       </c>
       <c r="P5" t="n">
-        <v>278.7782968440462</v>
+        <v>278.7684574895859</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16561,28 +16610,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1336140267572875</v>
+        <v>0.1358371458073279</v>
       </c>
       <c r="J6" t="n">
+        <v>318</v>
+      </c>
+      <c r="K6" t="n">
         <v>317</v>
       </c>
-      <c r="K6" t="n">
-        <v>316</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02231604540808751</v>
+        <v>0.02319560599773285</v>
       </c>
       <c r="M6" t="n">
-        <v>4.904405120301067</v>
+        <v>4.896554801635683</v>
       </c>
       <c r="N6" t="n">
-        <v>39.44072842257424</v>
+        <v>39.34996279292452</v>
       </c>
       <c r="O6" t="n">
-        <v>6.280185381226755</v>
+        <v>6.272954869351805</v>
       </c>
       <c r="P6" t="n">
-        <v>282.6667753138323</v>
+        <v>282.642135034672</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16639,28 +16688,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1142716454489732</v>
+        <v>0.1150551481301159</v>
       </c>
       <c r="J7" t="n">
+        <v>318</v>
+      </c>
+      <c r="K7" t="n">
         <v>317</v>
       </c>
-      <c r="K7" t="n">
-        <v>316</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01786108548637055</v>
+        <v>0.01823250716519575</v>
       </c>
       <c r="M7" t="n">
-        <v>4.719329659143863</v>
+        <v>4.708036725439808</v>
       </c>
       <c r="N7" t="n">
-        <v>36.20775539623028</v>
+        <v>36.09771538583809</v>
       </c>
       <c r="O7" t="n">
-        <v>6.017288043315716</v>
+        <v>6.008137430671679</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6037962445411</v>
+        <v>295.5951121730399</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16717,28 +16766,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09652590994023143</v>
+        <v>0.09851548101000718</v>
       </c>
       <c r="J8" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01074370478535991</v>
+        <v>0.01126134487165598</v>
       </c>
       <c r="M8" t="n">
-        <v>5.36535015024493</v>
+        <v>5.357777027605287</v>
       </c>
       <c r="N8" t="n">
-        <v>43.37126382417383</v>
+        <v>43.26106765796632</v>
       </c>
       <c r="O8" t="n">
-        <v>6.585686283461567</v>
+        <v>6.57731462361094</v>
       </c>
       <c r="P8" t="n">
-        <v>297.5258528056606</v>
+        <v>297.5038128887521</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16795,28 +16844,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.187965854694511</v>
+        <v>0.1898578030438134</v>
       </c>
       <c r="J9" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04870836619965979</v>
+        <v>0.04996184857360553</v>
       </c>
       <c r="M9" t="n">
-        <v>4.577300301075919</v>
+        <v>4.571401528568062</v>
       </c>
       <c r="N9" t="n">
-        <v>34.88410258463632</v>
+        <v>34.79817466548661</v>
       </c>
       <c r="O9" t="n">
-        <v>5.906276541496878</v>
+        <v>5.89899776788283</v>
       </c>
       <c r="P9" t="n">
-        <v>300.5301898546601</v>
+        <v>300.5092313751931</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16873,28 +16922,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01405271192629477</v>
+        <v>0.0140712339113791</v>
       </c>
       <c r="J10" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K10" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001312377471650583</v>
+        <v>0.0001325611573346208</v>
       </c>
       <c r="M10" t="n">
-        <v>6.532813353190098</v>
+        <v>6.51224504335481</v>
       </c>
       <c r="N10" t="n">
-        <v>76.06135069457191</v>
+        <v>75.82065256245021</v>
       </c>
       <c r="O10" t="n">
-        <v>8.721315880907646</v>
+        <v>8.707505530428918</v>
       </c>
       <c r="P10" t="n">
-        <v>306.0586659692053</v>
+        <v>306.058460787788</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16932,7 +16981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K318"/>
+  <dimension ref="A1:K319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35013,6 +35062,63 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.560182010660945,174.50871874527232</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.5607396626214,174.50800304699519</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.561494484114846,174.5075868762618</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.562294277224154,174.5073187463817</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-35.56312226620037,174.50725644742337</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-35.56401336529636,174.50747273031317</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-35.56479661528628,174.5080691379001</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-35.56538232354695,174.50887913348356</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-35.565735907331394,174.50974074309195</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K319"/>
+  <dimension ref="A1:K320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12861,6 +12861,45 @@
         <v>306.46</v>
       </c>
       <c r="K319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>311.95</v>
+      </c>
+      <c r="C320" t="n">
+        <v>286.73</v>
+      </c>
+      <c r="D320" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="E320" t="n">
+        <v>282.63</v>
+      </c>
+      <c r="F320" t="n">
+        <v>289.42</v>
+      </c>
+      <c r="G320" t="n">
+        <v>296.81</v>
+      </c>
+      <c r="H320" t="n">
+        <v>301.21</v>
+      </c>
+      <c r="I320" t="n">
+        <v>303.87</v>
+      </c>
+      <c r="J320" t="n">
+        <v>306.45</v>
+      </c>
+      <c r="K320" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12877,7 +12916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16130,6 +16169,16 @@
       </c>
       <c r="B325" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -16298,28 +16347,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1108206567215052</v>
+        <v>0.1106635870723361</v>
       </c>
       <c r="J2" t="n">
+        <v>319</v>
+      </c>
+      <c r="K2" t="n">
         <v>318</v>
       </c>
-      <c r="K2" t="n">
-        <v>317</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01806228226270679</v>
+        <v>0.01814296226758572</v>
       </c>
       <c r="M2" t="n">
-        <v>4.557295530322479</v>
+        <v>4.54371831183087</v>
       </c>
       <c r="N2" t="n">
-        <v>34.25739348634124</v>
+        <v>34.14983743618448</v>
       </c>
       <c r="O2" t="n">
-        <v>5.852981589441508</v>
+        <v>5.843786224374099</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2284759850105</v>
+        <v>309.2302097678009</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16376,28 +16425,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2145316886251446</v>
+        <v>0.2137799189591766</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06737016535917972</v>
+        <v>0.06738574475655756</v>
       </c>
       <c r="M3" t="n">
-        <v>4.445735699672177</v>
+        <v>4.4345718895714</v>
       </c>
       <c r="N3" t="n">
-        <v>32.60500410376095</v>
+        <v>32.50671032650314</v>
       </c>
       <c r="O3" t="n">
-        <v>5.710079167906602</v>
+        <v>5.701465629687084</v>
       </c>
       <c r="P3" t="n">
-        <v>282.1257224292924</v>
+        <v>282.134025930673</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16454,28 +16503,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2556101048098522</v>
+        <v>0.2535846551232945</v>
       </c>
       <c r="J4" t="n">
+        <v>319</v>
+      </c>
+      <c r="K4" t="n">
         <v>318</v>
       </c>
-      <c r="K4" t="n">
-        <v>317</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0749204729388685</v>
+        <v>0.07428731413699607</v>
       </c>
       <c r="M4" t="n">
-        <v>5.043672420571111</v>
+        <v>5.037771223017045</v>
       </c>
       <c r="N4" t="n">
-        <v>40.85450432093718</v>
+        <v>40.75401984977541</v>
       </c>
       <c r="O4" t="n">
-        <v>6.391752836346003</v>
+        <v>6.38388751857169</v>
       </c>
       <c r="P4" t="n">
-        <v>281.7725121728087</v>
+        <v>281.7950370138656</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16532,28 +16581,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1887811901072252</v>
+        <v>0.1879866685060654</v>
       </c>
       <c r="J5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03795800190477427</v>
+        <v>0.03791753948704257</v>
       </c>
       <c r="M5" t="n">
-        <v>5.397325592053587</v>
+        <v>5.385406551088619</v>
       </c>
       <c r="N5" t="n">
-        <v>45.7210500033449</v>
+        <v>45.58112772201131</v>
       </c>
       <c r="O5" t="n">
-        <v>6.761734245246918</v>
+        <v>6.751379690256749</v>
       </c>
       <c r="P5" t="n">
-        <v>278.7684574895859</v>
+        <v>278.7773059901249</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16610,28 +16659,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1358371458073279</v>
+        <v>0.1379665286463752</v>
       </c>
       <c r="J6" t="n">
+        <v>319</v>
+      </c>
+      <c r="K6" t="n">
         <v>318</v>
       </c>
-      <c r="K6" t="n">
-        <v>317</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02319560599773285</v>
+        <v>0.02406643989495139</v>
       </c>
       <c r="M6" t="n">
-        <v>4.896554801635683</v>
+        <v>4.888362682453312</v>
       </c>
       <c r="N6" t="n">
-        <v>39.34996279292452</v>
+        <v>39.25715569595204</v>
       </c>
       <c r="O6" t="n">
-        <v>6.272954869351805</v>
+        <v>6.265553103753255</v>
       </c>
       <c r="P6" t="n">
-        <v>282.642135034672</v>
+        <v>282.6184543625146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16688,28 +16737,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1150551481301159</v>
+        <v>0.1137996811865373</v>
       </c>
       <c r="J7" t="n">
+        <v>319</v>
+      </c>
+      <c r="K7" t="n">
         <v>318</v>
       </c>
-      <c r="K7" t="n">
-        <v>317</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01823250716519575</v>
+        <v>0.01796919134451946</v>
       </c>
       <c r="M7" t="n">
-        <v>4.708036725439808</v>
+        <v>4.699101829186378</v>
       </c>
       <c r="N7" t="n">
-        <v>36.09771538583809</v>
+        <v>35.9949541141459</v>
       </c>
       <c r="O7" t="n">
-        <v>6.008137430671679</v>
+        <v>5.999579494776771</v>
       </c>
       <c r="P7" t="n">
-        <v>295.5951121730399</v>
+        <v>295.6090741063053</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16766,28 +16815,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09851548101000718</v>
+        <v>0.09923914710806271</v>
       </c>
       <c r="J8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K8" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01126134487165598</v>
+        <v>0.01150864326227363</v>
       </c>
       <c r="M8" t="n">
-        <v>5.357777027605287</v>
+        <v>5.344263708488276</v>
       </c>
       <c r="N8" t="n">
-        <v>43.26106765796632</v>
+        <v>43.12818359259776</v>
       </c>
       <c r="O8" t="n">
-        <v>6.57731462361094</v>
+        <v>6.567205158406257</v>
       </c>
       <c r="P8" t="n">
-        <v>297.5038128887521</v>
+        <v>297.4957692369541</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16844,28 +16893,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1898578030438134</v>
+        <v>0.1887010511377082</v>
       </c>
       <c r="J9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04996184857360553</v>
+        <v>0.04972179433846857</v>
       </c>
       <c r="M9" t="n">
-        <v>4.571401528568062</v>
+        <v>4.562478826621732</v>
       </c>
       <c r="N9" t="n">
-        <v>34.79817466548661</v>
+        <v>34.6975642088669</v>
       </c>
       <c r="O9" t="n">
-        <v>5.89899776788283</v>
+        <v>5.890463836479</v>
       </c>
       <c r="P9" t="n">
-        <v>300.5092313751931</v>
+        <v>300.5220888374598</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16922,28 +16971,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0140712339113791</v>
+        <v>0.01408361873897127</v>
       </c>
       <c r="J10" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001325611573346208</v>
+        <v>0.0001337831579022453</v>
       </c>
       <c r="M10" t="n">
-        <v>6.51224504335481</v>
+        <v>6.491771314898644</v>
       </c>
       <c r="N10" t="n">
-        <v>75.82065256245021</v>
+        <v>75.58147174352158</v>
       </c>
       <c r="O10" t="n">
-        <v>8.707505530428918</v>
+        <v>8.69376050645068</v>
       </c>
       <c r="P10" t="n">
-        <v>306.058460787788</v>
+        <v>306.0583231286645</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16981,7 +17030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K319"/>
+  <dimension ref="A1:K320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35119,6 +35168,63 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.56016966167335,174.5086930777402</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.560722328672966,174.5079603703925</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-35.56148549751036,174.50755136208733</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-35.56229081289871,174.50729194041924</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-35.56312226032571,174.50725545454247</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-35.56402179034779,174.50744139628088</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-35.5648067798593,174.50805337655848</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-35.565415371352046,174.50885111071972</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-35.56573598936563,174.50974069735543</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
